--- a/Result/profitability/2067.xlsx
+++ b/Result/profitability/2067.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM59"/>
+  <dimension ref="A1:AM60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7931,6 +7931,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2067</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>235</v>
+      </c>
+      <c r="D60" t="n">
+        <v>232</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-36</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-15.42%</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>-8</v>
+      </c>
+      <c r="J60" t="n">
+        <v>-45</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-39</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="M60" t="n">
+        <v>-0.7025</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3.9325</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W60" t="n">
+        <v>-0.1899999999999999</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0.2794117647058822</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>-0.7811816192560175</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0.0481927710843375</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>-6.04</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>-0.8579545454545454</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK60" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
